--- a/Figure 1/Mouse weight & GTT/Weight&GTTCohort2.xlsx
+++ b/Figure 1/Mouse weight & GTT/Weight&GTTCohort2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure 3\Mouse weight &amp; GTT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 1\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BE44A09-EE3B-4E90-886C-858EE95CAB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE33606-646E-4486-9FD4-C6588BDAA4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2197215B-64E2-46CD-9E46-6556A9BFA39E}"/>
+    <workbookView xWindow="9510" yWindow="2055" windowWidth="12690" windowHeight="11385" xr2:uid="{2197215B-64E2-46CD-9E46-6556A9BFA39E}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="1" r:id="rId1"/>
@@ -802,7 +802,7 @@
         <v>45540</v>
       </c>
       <c r="D17" s="1">
-        <v>36.700000000000003</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -816,7 +816,7 @@
         <v>45540</v>
       </c>
       <c r="D18" s="1">
-        <v>31.7</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -830,7 +830,7 @@
         <v>45540</v>
       </c>
       <c r="D19" s="1">
-        <v>36.5</v>
+        <v>32.799999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -844,7 +844,7 @@
         <v>45540</v>
       </c>
       <c r="D20" s="1">
-        <v>32.299999999999997</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -858,7 +858,7 @@
         <v>45540</v>
       </c>
       <c r="D21" s="1">
-        <v>34</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -6298,12 +6298,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6528,17 +6527,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FA683CE-1C66-495C-B415-AE7EB6D3803A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F7B0A92-6AE3-4754-A87C-9BC386EADEAF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="b159d527-15c9-467a-b762-1e479e1f7549"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6563,18 +6572,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F7B0A92-6AE3-4754-A87C-9BC386EADEAF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FA683CE-1C66-495C-B415-AE7EB6D3803A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="b159d527-15c9-467a-b762-1e479e1f7549"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Figure 1/Mouse weight & GTT/Weight&GTTCohort2.xlsx
+++ b/Figure 1/Mouse weight & GTT/Weight&GTTCohort2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 1\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE33606-646E-4486-9FD4-C6588BDAA4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7108A397-129D-4AF4-B3FA-34CA8A59C90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="2055" windowWidth="12690" windowHeight="11385" xr2:uid="{2197215B-64E2-46CD-9E46-6556A9BFA39E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2197215B-64E2-46CD-9E46-6556A9BFA39E}"/>
   </bookViews>
   <sheets>
     <sheet name="Weight" sheetId="1" r:id="rId1"/>
@@ -6298,11 +6298,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6527,27 +6528,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F7B0A92-6AE3-4754-A87C-9BC386EADEAF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FA683CE-1C66-495C-B415-AE7EB6D3803A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="b159d527-15c9-467a-b762-1e479e1f7549"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6572,9 +6563,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FA683CE-1C66-495C-B415-AE7EB6D3803A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F7B0A92-6AE3-4754-A87C-9BC386EADEAF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="b159d527-15c9-467a-b762-1e479e1f7549"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="afb2a5ad-58d9-4e2b-8927-e9e6a6f32944"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>